--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.17571897424422</v>
+        <v>8.966054333314686</v>
       </c>
       <c r="D2" t="n">
-        <v>54.49236663734435</v>
+        <v>8.855009578568458</v>
       </c>
       <c r="E2" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F2" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.65109318982316</v>
+        <v>7.580802643346264</v>
       </c>
       <c r="D3" t="n">
-        <v>46.19626455888782</v>
+        <v>7.506892990819271</v>
       </c>
       <c r="E3" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F3" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.44777236512685</v>
+        <v>7.060263009333114</v>
       </c>
       <c r="D4" t="n">
-        <v>42.52328744629195</v>
+        <v>6.910034210022442</v>
       </c>
       <c r="E4" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F4" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.1859517012988</v>
+        <v>7.505217151461055</v>
       </c>
       <c r="D5" t="n">
-        <v>45.19415887668082</v>
+        <v>7.344050817460633</v>
       </c>
       <c r="E5" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F5" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.47265571026066</v>
+        <v>6.901806552917358</v>
       </c>
       <c r="D6" t="n">
-        <v>41.46677459370331</v>
+        <v>6.738350871476787</v>
       </c>
       <c r="E6" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F6" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.97392196252247</v>
+        <v>5.033262318909903</v>
       </c>
       <c r="D7" t="n">
-        <v>30.46664698184614</v>
+        <v>4.950830134549998</v>
       </c>
       <c r="E7" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F7" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.1373725595361</v>
+        <v>5.709823040924616</v>
       </c>
       <c r="D8" t="n">
-        <v>34.6532302327446</v>
+        <v>5.631149912820997</v>
       </c>
       <c r="E8" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F8" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49007108955323</v>
+        <v>6.742136552052401</v>
       </c>
       <c r="D9" t="n">
-        <v>41.45827242981901</v>
+        <v>6.73696926984559</v>
       </c>
       <c r="E9" t="n">
-        <v>6.893611554296647</v>
+        <v>1.120211877573205</v>
       </c>
       <c r="F9" t="n">
-        <v>6.81624870948485</v>
+        <v>1.107640415291288</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
